--- a/BOMs/Full BOM.xlsx
+++ b/BOMs/Full BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Documents\GitHub\Recept-5GHz-FPV-Reciever\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Documents\GitHub\Recept-5GHz-FPV-Reciever\BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689F7AFC-FC82-4F6B-B5B5-B8FBBA2E8D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5729F1-254B-4B75-98B9-354AAAF474B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EFF6145-C92F-42FA-826A-16B1F20D9DDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>BOM LIST</t>
   </si>
@@ -47,9 +47,6 @@
     <t>RX5808 module</t>
   </si>
   <si>
-    <t>Antenna + 90 degree SMA</t>
-  </si>
-  <si>
     <t>Pounds</t>
   </si>
   <si>
@@ -60,6 +57,30 @@
   </si>
   <si>
     <t>Battery</t>
+  </si>
+  <si>
+    <t>90 degree SMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antenna </t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005006153683653.html</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005005665998117.html</t>
+  </si>
+  <si>
+    <t>https://www.ebay.co.uk/itm/264574341923</t>
+  </si>
+  <si>
+    <t>(This module is not cheaper on AliExpress)</t>
+  </si>
+  <si>
+    <t>(I don't feel safe buying batteries off Ali)</t>
+  </si>
+  <si>
+    <t>https://www.ebay.co.uk/itm/396305473532?var=665862385939</t>
   </si>
 </sst>
 </file>
@@ -67,8 +88,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="&quot;£&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -101,8 +122,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,26 +458,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09959730-F69C-4851-A061-89FC27E3F6C8}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="9.140625" style="2"/>
+    <col min="4" max="5" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -464,43 +485,72 @@
         <v>198.94</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>9.17</v>
+        <v>5.8</v>
       </c>
       <c r="D4" s="2">
-        <v>12.31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.77</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3.37</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4.51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C6" s="1">
         <v>24.98</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="2">
         <v>33.54</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2">
         <v>9.39</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2">
-        <f>D5+D4+D3+D6</f>
-        <v>254.18</v>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
+        <f>D6+D5+D3+D7</f>
+        <v>246.38</v>
       </c>
     </row>
   </sheetData>
